--- a/households_df_updated.xlsx
+++ b/households_df_updated.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,12 +429,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Predicted_Households</t>
         </is>
@@ -3841,7 +3853,7 @@
         <v>2026</v>
       </c>
       <c r="B428" t="n">
-        <v>2814005.976305037</v>
+        <v>2810189.930588571</v>
       </c>
     </row>
     <row r="429">
@@ -3849,7 +3861,7 @@
         <v>2027</v>
       </c>
       <c r="B429" t="n">
-        <v>2822781.026566667</v>
+        <v>2812583.760678769</v>
       </c>
     </row>
     <row r="430">
@@ -3857,7 +3869,7 @@
         <v>2028</v>
       </c>
       <c r="B430" t="n">
-        <v>2831376.83562009</v>
+        <v>2812308.130352888</v>
       </c>
     </row>
     <row r="431">
@@ -3865,7 +3877,7 @@
         <v>2029</v>
       </c>
       <c r="B431" t="n">
-        <v>2839796.470952686</v>
+        <v>2809455.121621833</v>
       </c>
     </row>
     <row r="432">
@@ -3873,7 +3885,7 @@
         <v>2030</v>
       </c>
       <c r="B432" t="n">
-        <v>2848042.984820931</v>
+        <v>2804129.21704847</v>
       </c>
     </row>
     <row r="433">
@@ -3881,7 +3893,7 @@
         <v>2031</v>
       </c>
       <c r="B433" t="n">
-        <v>2856119.411705716</v>
+        <v>2796445.567580564</v>
       </c>
     </row>
     <row r="434">
@@ -3889,7 +3901,7 @@
         <v>2032</v>
       </c>
       <c r="B434" t="n">
-        <v>2864028.765964559</v>
+        <v>2786528.217566779</v>
       </c>
     </row>
     <row r="435">
@@ -3897,7 +3909,7 @@
         <v>2033</v>
       </c>
       <c r="B435" t="n">
-        <v>2871774.039671132</v>
+        <v>2774508.327410652</v>
       </c>
     </row>
     <row r="436">
@@ -3905,7 +3917,7 @@
         <v>2034</v>
       </c>
       <c r="B436" t="n">
-        <v>2879358.200632727</v>
+        <v>2760522.430519555</v>
       </c>
     </row>
     <row r="437">
@@ -3913,7 +3925,7 @@
         <v>2035</v>
       </c>
       <c r="B437" t="n">
-        <v>2886784.190576565</v>
+        <v>2744710.756559326</v>
       </c>
     </row>
     <row r="438">
@@ -3921,7 +3933,7 @@
         <v>2036</v>
       </c>
       <c r="B438" t="n">
-        <v>2894054.923496118</v>
+        <v>2727215.647833718</v>
       </c>
     </row>
     <row r="439">
@@ -3929,7 +3941,7 @@
         <v>2037</v>
       </c>
       <c r="B439" t="n">
-        <v>2901173.284148874</v>
+        <v>2708180.090159754</v>
       </c>
     </row>
     <row r="440">
@@ -3937,7 +3949,7 @@
         <v>2038</v>
       </c>
       <c r="B440" t="n">
-        <v>2908142.126697267</v>
+        <v>2687746.374164476</v>
       </c>
     </row>
     <row r="441">
@@ -3945,7 +3957,7 @@
         <v>2039</v>
       </c>
       <c r="B441" t="n">
-        <v>2914964.273484802</v>
+        <v>2666054.897704146</v>
       </c>
     </row>
     <row r="442">
@@ -3953,7 +3965,7 @@
         <v>2040</v>
       </c>
       <c r="B442" t="n">
-        <v>2921642.513939664</v>
+        <v>2643243.115276322</v>
       </c>
     </row>
     <row r="443">
@@ -3961,7 +3973,7 @@
         <v>2041</v>
       </c>
       <c r="B443" t="n">
-        <v>2928179.603598444</v>
+        <v>2619444.635983658</v>
       </c>
     </row>
     <row r="444">
@@ -3969,7 +3981,7 @@
         <v>2042</v>
       </c>
       <c r="B444" t="n">
-        <v>2934578.263242869</v>
+        <v>2594788.467895102</v>
       </c>
     </row>
     <row r="445">
@@ -3977,7 +3989,7 @@
         <v>2043</v>
       </c>
       <c r="B445" t="n">
-        <v>2940841.178142744</v>
+        <v>2569398.403573254</v>
       </c>
     </row>
     <row r="446">
@@ -3985,7 +3997,7 @@
         <v>2044</v>
       </c>
       <c r="B446" t="n">
-        <v>2946970.997398588</v>
+        <v>2543392.539098836</v>
       </c>
     </row>
     <row r="447">
@@ -3993,7 +4005,7 @@
         <v>2045</v>
       </c>
       <c r="B447" t="n">
-        <v>2952970.333377753</v>
+        <v>2516882.91709884</v>
       </c>
     </row>
     <row r="448">
@@ -4001,7 +4013,7 @@
         <v>2046</v>
       </c>
       <c r="B448" t="n">
-        <v>2958841.761238085</v>
+        <v>2489975.283027149</v>
       </c>
     </row>
     <row r="449">
@@ -4009,7 +4021,7 @@
         <v>2047</v>
       </c>
       <c r="B449" t="n">
-        <v>2964587.818533459</v>
+        <v>2462768.943194203</v>
       </c>
     </row>
     <row r="450">
@@ -4017,7 +4029,7 @@
         <v>2048</v>
       </c>
       <c r="B450" t="n">
-        <v>2970211.004895803</v>
+        <v>2435356.712726269</v>
       </c>
     </row>
     <row r="451">
@@ -4025,7 +4037,7 @@
         <v>2049</v>
       </c>
       <c r="B451" t="n">
-        <v>2975713.78178848</v>
+        <v>2407824.941682393</v>
       </c>
     </row>
     <row r="452">
@@ -4033,7 +4045,7 @@
         <v>2050</v>
       </c>
       <c r="B452" t="n">
-        <v>2981098.572326158</v>
+        <v>2380253.607896743</v>
       </c>
     </row>
     <row r="453">
@@ -4041,7 +4053,7 @@
         <v>2051</v>
       </c>
       <c r="B453" t="n">
-        <v>2986367.761156526</v>
+        <v>2352716.46567816</v>
       </c>
     </row>
     <row r="454">
@@ -4049,7 +4061,7 @@
         <v>2052</v>
       </c>
       <c r="B454" t="n">
-        <v>2991523.694399502</v>
+        <v>2325281.240225778</v>
       </c>
     </row>
     <row r="455">
@@ -4057,7 +4069,7 @@
         <v>2053</v>
       </c>
       <c r="B455" t="n">
-        <v>2996568.679639734</v>
+        <v>2298009.858455588</v>
       </c>
     </row>
     <row r="456">
@@ -4065,7 +4077,7 @@
         <v>2054</v>
       </c>
       <c r="B456" t="n">
-        <v>3001504.985968503</v>
+        <v>2270958.707831501</v>
       </c>
     </row>
     <row r="457">
@@ -4073,7 +4085,7 @@
         <v>2055</v>
       </c>
       <c r="B457" t="n">
-        <v>3006334.844071278</v>
+        <v>2244178.915717738</v>
       </c>
     </row>
     <row r="458">
@@ -4081,7 +4093,7 @@
         <v>2056</v>
       </c>
       <c r="B458" t="n">
-        <v>3011060.446357417</v>
+        <v>2217716.64268667</v>
       </c>
     </row>
     <row r="459">
@@ -4089,7 +4101,7 @@
         <v>2057</v>
       </c>
       <c r="B459" t="n">
-        <v>3015683.947128712</v>
+        <v>2191613.384104038</v>
       </c>
     </row>
     <row r="460">
@@ -4097,7 +4109,7 @@
         <v>2058</v>
       </c>
       <c r="B460" t="n">
-        <v>3020207.462783614</v>
+        <v>2165906.275154525</v>
       </c>
     </row>
     <row r="461">
@@ -4105,7 +4117,7 @@
         <v>2059</v>
       </c>
       <c r="B461" t="n">
-        <v>3024633.072054236</v>
+        <v>2140628.39525312</v>
       </c>
     </row>
     <row r="462">
@@ -4113,7 +4125,7 @@
         <v>2060</v>
       </c>
       <c r="B462" t="n">
-        <v>3028962.816273313</v>
+        <v>2115809.068503963</v>
       </c>
     </row>
     <row r="463">
@@ -4121,7 +4133,7 @@
         <v>2061</v>
       </c>
       <c r="B463" t="n">
-        <v>3033198.69966853</v>
+        <v>2091474.157515151</v>
       </c>
     </row>
     <row r="464">
@@ -4129,7 +4141,7 @@
         <v>2062</v>
       </c>
       <c r="B464" t="n">
-        <v>3037342.689681767</v>
+        <v>2067646.348453933</v>
       </c>
     </row>
     <row r="465">
@@ -4137,7 +4149,7 @@
         <v>2063</v>
       </c>
       <c r="B465" t="n">
-        <v>3041396.717310938</v>
+        <v>2044345.425733798</v>
       </c>
     </row>
     <row r="466">
@@ -4145,7 +4157,7 @@
         <v>2064</v>
       </c>
       <c r="B466" t="n">
-        <v>3045362.677472258</v>
+        <v>2021588.535165822</v>
       </c>
     </row>
     <row r="467">
@@ -4153,7 +4165,7 @@
         <v>2065</v>
       </c>
       <c r="B467" t="n">
-        <v>3049242.429380931</v>
+        <v>1999390.43478565</v>
       </c>
     </row>
     <row r="468">
@@ -4161,7 +4173,7 @@
         <v>2066</v>
       </c>
       <c r="B468" t="n">
-        <v>3053037.796948335</v>
+        <v>1977763.732889579</v>
       </c>
     </row>
     <row r="469">
@@ -4169,7 +4181,7 @@
         <v>2067</v>
       </c>
       <c r="B469" t="n">
-        <v>3056750.569193918</v>
+        <v>1956719.11308349</v>
       </c>
     </row>
     <row r="470">
@@ -4177,7 +4189,7 @@
         <v>2068</v>
       </c>
       <c r="B470" t="n">
-        <v>3060382.500670163</v>
+        <v>1936265.546372502</v>
       </c>
     </row>
     <row r="471">
@@ -4185,7 +4197,7 @@
         <v>2069</v>
       </c>
       <c r="B471" t="n">
-        <v>3063935.311899039</v>
+        <v>1916410.490502394</v>
       </c>
     </row>
     <row r="472">
@@ -4193,7 +4205,7 @@
         <v>2070</v>
       </c>
       <c r="B472" t="n">
-        <v>3067410.689818503</v>
+        <v>1897160.076911331</v>
       </c>
     </row>
     <row r="473">
@@ -4201,7 +4213,7 @@
         <v>2071</v>
       </c>
       <c r="B473" t="n">
-        <v>3070810.288237679</v>
+        <v>1878519.285767089</v>
       </c>
     </row>
     <row r="474">
@@ -4209,7 +4221,7 @@
         <v>2072</v>
       </c>
       <c r="B474" t="n">
-        <v>3074135.728299456</v>
+        <v>1860492.109655323</v>
       </c>
     </row>
     <row r="475">
@@ -4217,7 +4229,7 @@
         <v>2073</v>
       </c>
       <c r="B475" t="n">
-        <v>3077388.598949335</v>
+        <v>1843081.706552705</v>
       </c>
     </row>
     <row r="476">
@@ -4225,7 +4237,7 @@
         <v>2074</v>
       </c>
       <c r="B476" t="n">
-        <v>3080570.457409412</v>
+        <v>1826290.54276859</v>
       </c>
     </row>
     <row r="477">
@@ -4233,7 +4245,7 @@
         <v>2075</v>
       </c>
       <c r="B477" t="n">
-        <v>3083682.829656494</v>
+        <v>1810120.526573744</v>
       </c>
     </row>
     <row r="478">
@@ -4241,7 +4253,7 @@
         <v>2076</v>
       </c>
       <c r="B478" t="n">
-        <v>3086727.210903388</v>
+        <v>1794573.133257575</v>
       </c>
     </row>
     <row r="479">
@@ -4249,7 +4261,7 @@
         <v>2077</v>
       </c>
       <c r="B479" t="n">
-        <v>3089705.066082494</v>
+        <v>1779649.522368799</v>
       </c>
     </row>
     <row r="480">
@@ -4257,7 +4269,7 @@
         <v>2078</v>
       </c>
       <c r="B480" t="n">
-        <v>3092617.830330903</v>
+        <v>1765350.647901068</v>
       </c>
     </row>
     <row r="481">
@@ -4265,7 +4277,7 @@
         <v>2079</v>
       </c>
       <c r="B481" t="n">
-        <v>3095466.909476201</v>
+        <v>1751677.362186627</v>
       </c>
     </row>
     <row r="482">
@@ -4273,7 +4285,7 @@
         <v>2080</v>
       </c>
       <c r="B482" t="n">
-        <v>3098253.68052235</v>
+        <v>1738630.514259604</v>
       </c>
     </row>
     <row r="483">
@@ -4281,7 +4293,7 @@
         <v>2081</v>
       </c>
       <c r="B483" t="n">
-        <v>3100979.492134962</v>
+        <v>1726211.043447441</v>
       </c>
     </row>
     <row r="484">
@@ -4289,7 +4301,7 @@
         <v>2082</v>
       </c>
       <c r="B484" t="n">
-        <v>3103645.665125369</v>
+        <v>1714420.068945847</v>
       </c>
     </row>
     <row r="485">
@@ -4297,7 +4309,7 @@
         <v>2083</v>
       </c>
       <c r="B485" t="n">
-        <v>3106253.492933006</v>
+        <v>1703258.976130668</v>
       </c>
     </row>
     <row r="486">
@@ -4305,7 +4317,7 @@
         <v>2084</v>
       </c>
       <c r="B486" t="n">
-        <v>3108804.242105519</v>
+        <v>1692729.500360487</v>
       </c>
     </row>
     <row r="487">
@@ -4313,7 +4325,7 @@
         <v>2085</v>
       </c>
       <c r="B487" t="n">
-        <v>3111299.152776225</v>
+        <v>1682833.809027594</v>
       </c>
     </row>
     <row r="488">
@@ -4321,7 +4333,7 @@
         <v>2086</v>
       </c>
       <c r="B488" t="n">
-        <v>3113739.439138462</v>
+        <v>1673574.582623388</v>
       </c>
     </row>
     <row r="489">
@@ -4329,7 +4341,7 @@
         <v>2087</v>
       </c>
       <c r="B489" t="n">
-        <v>3116126.289916458</v>
+        <v>1664955.095598249</v>
       </c>
     </row>
     <row r="490">
@@ -4337,7 +4349,7 @@
         <v>2088</v>
       </c>
       <c r="B490" t="n">
-        <v>3118460.868832381</v>
+        <v>1656979.297816596</v>
       </c>
     </row>
     <row r="491">
@@ -4345,7 +4357,7 @@
         <v>2089</v>
       </c>
       <c r="B491" t="n">
-        <v>3120744.315069241</v>
+        <v>1649651.897436388</v>
       </c>
     </row>
     <row r="492">
@@ -4353,7 +4365,7 @@
         <v>2090</v>
       </c>
       <c r="B492" t="n">
-        <v>3122977.74372938</v>
+        <v>1642978.446079961</v>
       </c>
     </row>
     <row r="493">
@@ -4361,7 +4373,7 @@
         <v>2091</v>
       </c>
       <c r="B493" t="n">
-        <v>3125162.246288286</v>
+        <v>1636965.427211259</v>
       </c>
     </row>
     <row r="494">
@@ -4369,7 +4381,7 @@
         <v>2092</v>
       </c>
       <c r="B494" t="n">
-        <v>3127298.891043479</v>
+        <v>1631620.348694895</v>
       </c>
     </row>
     <row r="495">
@@ -4377,7 +4389,7 @@
         <v>2093</v>
       </c>
       <c r="B495" t="n">
-        <v>3129388.723558319</v>
+        <v>1626951.840586778</v>
       </c>
     </row>
     <row r="496">
@@ -4385,7 +4397,7 @@
         <v>2094</v>
       </c>
       <c r="B496" t="n">
-        <v>3131432.767100499</v>
+        <v>1622969.759296661</v>
       </c>
     </row>
     <row r="497">
@@ -4393,7 +4405,7 @@
         <v>2095</v>
       </c>
       <c r="B497" t="n">
-        <v>3133432.023075086</v>
+        <v>1619685.299372376</v>
       </c>
     </row>
     <row r="498">
@@ -4401,7 +4413,7 @@
         <v>2096</v>
       </c>
       <c r="B498" t="n">
-        <v>3135387.471451978</v>
+        <v>1617111.11428682</v>
       </c>
     </row>
     <row r="499">
@@ -4409,7 +4421,7 @@
         <v>2097</v>
       </c>
       <c r="B499" t="n">
-        <v>3137300.071187636</v>
+        <v>1615261.447765752</v>
       </c>
     </row>
     <row r="500">
@@ -4417,7 +4429,7 @@
         <v>2098</v>
       </c>
       <c r="B500" t="n">
-        <v>3139170.76064101</v>
+        <v>1614152.277381527</v>
       </c>
     </row>
     <row r="501">
@@ -4425,7 +4437,7 @@
         <v>2099</v>
       </c>
       <c r="B501" t="n">
-        <v>3141000.457983526</v>
+        <v>1613801.472360448</v>
       </c>
     </row>
     <row r="502">
@@ -4433,7 +4445,7 @@
         <v>2100</v>
       </c>
       <c r="B502" t="n">
-        <v>3142790.061603132</v>
+        <v>1614228.967816063</v>
       </c>
     </row>
   </sheetData>

--- a/households_df_updated.xlsx
+++ b/households_df_updated.xlsx
@@ -3853,7 +3853,7 @@
         <v>2026</v>
       </c>
       <c r="B428" t="n">
-        <v>2810189.930588571</v>
+        <v>2814005.976305037</v>
       </c>
     </row>
     <row r="429">
@@ -3861,7 +3861,7 @@
         <v>2027</v>
       </c>
       <c r="B429" t="n">
-        <v>2812583.760678769</v>
+        <v>2822781.026566667</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>2028</v>
       </c>
       <c r="B430" t="n">
-        <v>2812308.130352888</v>
+        <v>2831376.83562009</v>
       </c>
     </row>
     <row r="431">
@@ -3877,7 +3877,7 @@
         <v>2029</v>
       </c>
       <c r="B431" t="n">
-        <v>2809455.121621833</v>
+        <v>2839796.470952686</v>
       </c>
     </row>
     <row r="432">
@@ -3885,7 +3885,7 @@
         <v>2030</v>
       </c>
       <c r="B432" t="n">
-        <v>2804129.21704847</v>
+        <v>2848042.984820931</v>
       </c>
     </row>
     <row r="433">
@@ -3893,7 +3893,7 @@
         <v>2031</v>
       </c>
       <c r="B433" t="n">
-        <v>2796445.567580564</v>
+        <v>2856119.411705716</v>
       </c>
     </row>
     <row r="434">
@@ -3901,7 +3901,7 @@
         <v>2032</v>
       </c>
       <c r="B434" t="n">
-        <v>2786528.217566779</v>
+        <v>2864028.765964559</v>
       </c>
     </row>
     <row r="435">
@@ -3909,7 +3909,7 @@
         <v>2033</v>
       </c>
       <c r="B435" t="n">
-        <v>2774508.327410652</v>
+        <v>2871774.039671132</v>
       </c>
     </row>
     <row r="436">
@@ -3917,7 +3917,7 @@
         <v>2034</v>
       </c>
       <c r="B436" t="n">
-        <v>2760522.430519555</v>
+        <v>2879358.200632727</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>2035</v>
       </c>
       <c r="B437" t="n">
-        <v>2744710.756559326</v>
+        <v>2886784.190576565</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>2036</v>
       </c>
       <c r="B438" t="n">
-        <v>2727215.647833718</v>
+        <v>2894054.923496118</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>2037</v>
       </c>
       <c r="B439" t="n">
-        <v>2708180.090159754</v>
+        <v>2901173.284148874</v>
       </c>
     </row>
     <row r="440">
@@ -3949,7 +3949,7 @@
         <v>2038</v>
       </c>
       <c r="B440" t="n">
-        <v>2687746.374164476</v>
+        <v>2908142.126697267</v>
       </c>
     </row>
     <row r="441">
@@ -3957,7 +3957,7 @@
         <v>2039</v>
       </c>
       <c r="B441" t="n">
-        <v>2666054.897704146</v>
+        <v>2914964.273484802</v>
       </c>
     </row>
     <row r="442">
@@ -3965,7 +3965,7 @@
         <v>2040</v>
       </c>
       <c r="B442" t="n">
-        <v>2643243.115276322</v>
+        <v>2921642.513939664</v>
       </c>
     </row>
     <row r="443">
@@ -3973,7 +3973,7 @@
         <v>2041</v>
       </c>
       <c r="B443" t="n">
-        <v>2619444.635983658</v>
+        <v>2928179.603598444</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>2042</v>
       </c>
       <c r="B444" t="n">
-        <v>2594788.467895102</v>
+        <v>2934578.263242869</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>2043</v>
       </c>
       <c r="B445" t="n">
-        <v>2569398.403573254</v>
+        <v>2940841.178142744</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>2044</v>
       </c>
       <c r="B446" t="n">
-        <v>2543392.539098836</v>
+        <v>2946970.997398588</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>2045</v>
       </c>
       <c r="B447" t="n">
-        <v>2516882.91709884</v>
+        <v>2952970.333377753</v>
       </c>
     </row>
     <row r="448">
@@ -4013,7 +4013,7 @@
         <v>2046</v>
       </c>
       <c r="B448" t="n">
-        <v>2489975.283027149</v>
+        <v>2958841.761238085</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>2047</v>
       </c>
       <c r="B449" t="n">
-        <v>2462768.943194203</v>
+        <v>2964587.818533459</v>
       </c>
     </row>
     <row r="450">
@@ -4029,7 +4029,7 @@
         <v>2048</v>
       </c>
       <c r="B450" t="n">
-        <v>2435356.712726269</v>
+        <v>2970211.004895803</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>2049</v>
       </c>
       <c r="B451" t="n">
-        <v>2407824.941682393</v>
+        <v>2975713.78178848</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>2050</v>
       </c>
       <c r="B452" t="n">
-        <v>2380253.607896743</v>
+        <v>2981098.572326158</v>
       </c>
     </row>
     <row r="453">
@@ -4053,7 +4053,7 @@
         <v>2051</v>
       </c>
       <c r="B453" t="n">
-        <v>2352716.46567816</v>
+        <v>2986367.761156526</v>
       </c>
     </row>
     <row r="454">
@@ -4061,7 +4061,7 @@
         <v>2052</v>
       </c>
       <c r="B454" t="n">
-        <v>2325281.240225778</v>
+        <v>2991523.694399502</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>2053</v>
       </c>
       <c r="B455" t="n">
-        <v>2298009.858455588</v>
+        <v>2996568.679639734</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>2054</v>
       </c>
       <c r="B456" t="n">
-        <v>2270958.707831501</v>
+        <v>3001504.985968503</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>2055</v>
       </c>
       <c r="B457" t="n">
-        <v>2244178.915717738</v>
+        <v>3006334.844071278</v>
       </c>
     </row>
     <row r="458">
@@ -4093,7 +4093,7 @@
         <v>2056</v>
       </c>
       <c r="B458" t="n">
-        <v>2217716.64268667</v>
+        <v>3011060.446357417</v>
       </c>
     </row>
     <row r="459">
@@ -4101,7 +4101,7 @@
         <v>2057</v>
       </c>
       <c r="B459" t="n">
-        <v>2191613.384104038</v>
+        <v>3015683.947128712</v>
       </c>
     </row>
     <row r="460">
@@ -4109,7 +4109,7 @@
         <v>2058</v>
       </c>
       <c r="B460" t="n">
-        <v>2165906.275154525</v>
+        <v>3020207.462783614</v>
       </c>
     </row>
     <row r="461">
@@ -4117,7 +4117,7 @@
         <v>2059</v>
       </c>
       <c r="B461" t="n">
-        <v>2140628.39525312</v>
+        <v>3024633.072054236</v>
       </c>
     </row>
     <row r="462">
@@ -4125,7 +4125,7 @@
         <v>2060</v>
       </c>
       <c r="B462" t="n">
-        <v>2115809.068503963</v>
+        <v>3028962.816273313</v>
       </c>
     </row>
     <row r="463">
@@ -4133,7 +4133,7 @@
         <v>2061</v>
       </c>
       <c r="B463" t="n">
-        <v>2091474.157515151</v>
+        <v>3033198.69966853</v>
       </c>
     </row>
     <row r="464">
@@ -4141,7 +4141,7 @@
         <v>2062</v>
       </c>
       <c r="B464" t="n">
-        <v>2067646.348453933</v>
+        <v>3037342.689681767</v>
       </c>
     </row>
     <row r="465">
@@ -4149,7 +4149,7 @@
         <v>2063</v>
       </c>
       <c r="B465" t="n">
-        <v>2044345.425733798</v>
+        <v>3041396.717310938</v>
       </c>
     </row>
     <row r="466">
@@ -4157,7 +4157,7 @@
         <v>2064</v>
       </c>
       <c r="B466" t="n">
-        <v>2021588.535165822</v>
+        <v>3045362.677472258</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>2065</v>
       </c>
       <c r="B467" t="n">
-        <v>1999390.43478565</v>
+        <v>3049242.429380931</v>
       </c>
     </row>
     <row r="468">
@@ -4173,7 +4173,7 @@
         <v>2066</v>
       </c>
       <c r="B468" t="n">
-        <v>1977763.732889579</v>
+        <v>3053037.796948335</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>2067</v>
       </c>
       <c r="B469" t="n">
-        <v>1956719.11308349</v>
+        <v>3056750.569193918</v>
       </c>
     </row>
     <row r="470">
@@ -4189,7 +4189,7 @@
         <v>2068</v>
       </c>
       <c r="B470" t="n">
-        <v>1936265.546372502</v>
+        <v>3060382.500670163</v>
       </c>
     </row>
     <row r="471">
@@ -4197,7 +4197,7 @@
         <v>2069</v>
       </c>
       <c r="B471" t="n">
-        <v>1916410.490502394</v>
+        <v>3063935.311899039</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>2070</v>
       </c>
       <c r="B472" t="n">
-        <v>1897160.076911331</v>
+        <v>3067410.689818503</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>2071</v>
       </c>
       <c r="B473" t="n">
-        <v>1878519.285767089</v>
+        <v>3070810.288237679</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>2072</v>
       </c>
       <c r="B474" t="n">
-        <v>1860492.109655323</v>
+        <v>3074135.728299456</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>2073</v>
       </c>
       <c r="B475" t="n">
-        <v>1843081.706552705</v>
+        <v>3077388.598949335</v>
       </c>
     </row>
     <row r="476">
@@ -4237,7 +4237,7 @@
         <v>2074</v>
       </c>
       <c r="B476" t="n">
-        <v>1826290.54276859</v>
+        <v>3080570.457409412</v>
       </c>
     </row>
     <row r="477">
@@ -4245,7 +4245,7 @@
         <v>2075</v>
       </c>
       <c r="B477" t="n">
-        <v>1810120.526573744</v>
+        <v>3083682.829656494</v>
       </c>
     </row>
     <row r="478">
@@ -4253,7 +4253,7 @@
         <v>2076</v>
       </c>
       <c r="B478" t="n">
-        <v>1794573.133257575</v>
+        <v>3086727.210903388</v>
       </c>
     </row>
     <row r="479">
@@ -4261,7 +4261,7 @@
         <v>2077</v>
       </c>
       <c r="B479" t="n">
-        <v>1779649.522368799</v>
+        <v>3089705.066082494</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>2078</v>
       </c>
       <c r="B480" t="n">
-        <v>1765350.647901068</v>
+        <v>3092617.830330903</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>2079</v>
       </c>
       <c r="B481" t="n">
-        <v>1751677.362186627</v>
+        <v>3095466.909476201</v>
       </c>
     </row>
     <row r="482">
@@ -4285,7 +4285,7 @@
         <v>2080</v>
       </c>
       <c r="B482" t="n">
-        <v>1738630.514259604</v>
+        <v>3098253.68052235</v>
       </c>
     </row>
     <row r="483">
@@ -4293,7 +4293,7 @@
         <v>2081</v>
       </c>
       <c r="B483" t="n">
-        <v>1726211.043447441</v>
+        <v>3100979.492134962</v>
       </c>
     </row>
     <row r="484">
@@ -4301,7 +4301,7 @@
         <v>2082</v>
       </c>
       <c r="B484" t="n">
-        <v>1714420.068945847</v>
+        <v>3103645.665125369</v>
       </c>
     </row>
     <row r="485">
@@ -4309,7 +4309,7 @@
         <v>2083</v>
       </c>
       <c r="B485" t="n">
-        <v>1703258.976130668</v>
+        <v>3106253.492933006</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>2084</v>
       </c>
       <c r="B486" t="n">
-        <v>1692729.500360487</v>
+        <v>3108804.242105519</v>
       </c>
     </row>
     <row r="487">
@@ -4325,7 +4325,7 @@
         <v>2085</v>
       </c>
       <c r="B487" t="n">
-        <v>1682833.809027594</v>
+        <v>3111299.152776225</v>
       </c>
     </row>
     <row r="488">
@@ -4333,7 +4333,7 @@
         <v>2086</v>
       </c>
       <c r="B488" t="n">
-        <v>1673574.582623388</v>
+        <v>3113739.439138462</v>
       </c>
     </row>
     <row r="489">
@@ -4341,7 +4341,7 @@
         <v>2087</v>
       </c>
       <c r="B489" t="n">
-        <v>1664955.095598249</v>
+        <v>3116126.289916458</v>
       </c>
     </row>
     <row r="490">
@@ -4349,7 +4349,7 @@
         <v>2088</v>
       </c>
       <c r="B490" t="n">
-        <v>1656979.297816596</v>
+        <v>3118460.868832381</v>
       </c>
     </row>
     <row r="491">
@@ -4357,7 +4357,7 @@
         <v>2089</v>
       </c>
       <c r="B491" t="n">
-        <v>1649651.897436388</v>
+        <v>3120744.315069241</v>
       </c>
     </row>
     <row r="492">
@@ -4365,7 +4365,7 @@
         <v>2090</v>
       </c>
       <c r="B492" t="n">
-        <v>1642978.446079961</v>
+        <v>3122977.74372938</v>
       </c>
     </row>
     <row r="493">
@@ -4373,7 +4373,7 @@
         <v>2091</v>
       </c>
       <c r="B493" t="n">
-        <v>1636965.427211259</v>
+        <v>3125162.246288286</v>
       </c>
     </row>
     <row r="494">
@@ -4381,7 +4381,7 @@
         <v>2092</v>
       </c>
       <c r="B494" t="n">
-        <v>1631620.348694895</v>
+        <v>3127298.891043479</v>
       </c>
     </row>
     <row r="495">
@@ -4389,7 +4389,7 @@
         <v>2093</v>
       </c>
       <c r="B495" t="n">
-        <v>1626951.840586778</v>
+        <v>3129388.723558319</v>
       </c>
     </row>
     <row r="496">
@@ -4397,7 +4397,7 @@
         <v>2094</v>
       </c>
       <c r="B496" t="n">
-        <v>1622969.759296661</v>
+        <v>3131432.767100499</v>
       </c>
     </row>
     <row r="497">
@@ -4405,7 +4405,7 @@
         <v>2095</v>
       </c>
       <c r="B497" t="n">
-        <v>1619685.299372376</v>
+        <v>3133432.023075086</v>
       </c>
     </row>
     <row r="498">
@@ -4413,7 +4413,7 @@
         <v>2096</v>
       </c>
       <c r="B498" t="n">
-        <v>1617111.11428682</v>
+        <v>3135387.471451978</v>
       </c>
     </row>
     <row r="499">
@@ -4421,7 +4421,7 @@
         <v>2097</v>
       </c>
       <c r="B499" t="n">
-        <v>1615261.447765752</v>
+        <v>3137300.071187636</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>2098</v>
       </c>
       <c r="B500" t="n">
-        <v>1614152.277381527</v>
+        <v>3139170.76064101</v>
       </c>
     </row>
     <row r="501">
@@ -4437,7 +4437,7 @@
         <v>2099</v>
       </c>
       <c r="B501" t="n">
-        <v>1613801.472360448</v>
+        <v>3141000.457983526</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>2100</v>
       </c>
       <c r="B502" t="n">
-        <v>1614228.967816063</v>
+        <v>3142790.061603132</v>
       </c>
     </row>
   </sheetData>
